--- a/logs/Pasta1.xlsx
+++ b/logs/Pasta1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\I\Documents\GitHub\auto-reply-for-WhatsApp\logs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A3D0BE0-5E63-46F2-A47E-13A70FB6C3EA}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5F4CFC1-3A39-4906-932D-D6D8E266C2F1}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11805" xr2:uid="{9795C6AE-129E-4FBE-AA73-E7F14A523CEB}"/>
   </bookViews>
@@ -413,7 +413,7 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>1136473844</v>
+        <v>136473844</v>
       </c>
       <c r="B2" t="s">
         <v>3</v>
